--- a/educhrono-backend/app/templates/teaching-load_template_new.xlsx
+++ b/educhrono-backend/app/templates/teaching-load_template_new.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\FunctionX\educhrono-backend\app\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\FunctionX\educhrono\educhrono-backend\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5110C1-D9E9-4DD4-9AA2-A000F567EF63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155F8127-8C42-48C0-9437-F9B2F6190463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19260" windowHeight="10800" xr2:uid="{5B5DBAAC-C631-45FA-B853-65CC98287675}"/>
+    <workbookView xWindow="100" yWindow="0" windowWidth="19100" windowHeight="10800" xr2:uid="{5B5DBAAC-C631-45FA-B853-65CC98287675}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -185,10 +185,10 @@
     <t>Prof. Manoj Tyagi</t>
   </si>
   <si>
-    <t>CEO</t>
-  </si>
-  <si>
     <t>PDP</t>
+  </si>
+  <si>
+    <t>COE</t>
   </si>
 </sst>
 </file>
@@ -589,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D7A7487-AB41-41C7-A3A6-764F9E983796}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
@@ -622,10 +622,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>5</v>
@@ -651,13 +651,13 @@
         <v>33</v>
       </c>
       <c r="C2" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
         <v>1</v>
-      </c>
-      <c r="E2" s="1">
-        <v>2</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -730,10 +730,10 @@
         <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -765,13 +765,13 @@
         <v>25</v>
       </c>
       <c r="C5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>11</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -841,13 +841,13 @@
         <v>17</v>
       </c>
       <c r="C7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="1">
         <v>3</v>
@@ -984,34 +984,6 @@
       <c r="L10" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L10" xr:uid="{8D7A7487-AB41-41C7-A3A6-764F9E983796}">

--- a/educhrono-backend/app/templates/teaching-load_template_new.xlsx
+++ b/educhrono-backend/app/templates/teaching-load_template_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\FunctionX\educhrono\educhrono-backend\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155F8127-8C42-48C0-9437-F9B2F6190463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EDCDCB-8673-4F28-A70C-7FA97517C087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="100" yWindow="0" windowWidth="19100" windowHeight="10800" xr2:uid="{5B5DBAAC-C631-45FA-B853-65CC98287675}"/>
   </bookViews>
@@ -651,10 +651,10 @@
         <v>33</v>
       </c>
       <c r="C2" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -730,7 +730,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -765,7 +765,7 @@
         <v>25</v>
       </c>
       <c r="C5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -803,7 +803,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -841,7 +841,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -879,7 +879,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
